--- a/LubanLaunchConfig/Datas/LaunchConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\gt_jogosup777\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -110,9 +110,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>MagicWealthRes</t>
-  </si>
-  <si>
     <t>SJYT20175638FDUUKNS38393753029039V32f700</t>
   </si>
   <si>
@@ -132,6 +129,10 @@
   </si>
   <si>
     <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>JogosUpRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -582,7 +583,7 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="42.625" customWidth="1"/>
+    <col min="3" max="3" width="49.25" customWidth="1"/>
     <col min="4" max="4" width="22.875" customWidth="1"/>
     <col min="5" max="5" width="44.875" customWidth="1"/>
     <col min="6" max="6" width="19.375" customWidth="1"/>
@@ -721,31 +722,31 @@
         <v>28</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="M4" s="1">
         <v>9</v>

--- a/LubanLaunchConfig/Datas/LaunchConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\DoubleJackpotClub\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -110,9 +110,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>MagicWealthRes</t>
-  </si>
-  <si>
     <t>SJYT20175638FDUUKNS38393753029039V32f700</t>
   </si>
   <si>
@@ -132,6 +129,10 @@
   </si>
   <si>
     <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoubleJackpotClubRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -721,31 +722,31 @@
         <v>28</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="M4" s="1">
         <v>9</v>

--- a/LubanLaunchConfig/Datas/LaunchConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchConfig.xlsx
@@ -128,11 +128,11 @@
     <t>English</t>
   </si>
   <si>
-    <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <t>DoubleJackpotClubRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>DoubleJackpotClubRes</t>
+    <t>https://slotapp.s3.amazonaws.com</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -722,10 +722,10 @@
         <v>28</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>29</v>

--- a/LubanLaunchConfig/Datas/LaunchConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_CandyVegas\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -110,9 +110,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>MagicWealthRes</t>
-  </si>
-  <si>
     <t>SJYT20175638FDUUKNS38393753029039V32f700</t>
   </si>
   <si>
@@ -132,6 +129,10 @@
   </si>
   <si>
     <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CandyVegasRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -721,31 +722,31 @@
         <v>28</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="M4" s="1">
         <v>9</v>

--- a/LubanLaunchConfig/Datas/LaunchConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchConfig.xlsx
@@ -128,7 +128,7 @@
     <t>English</t>
   </si>
   <si>
-    <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <t>https://awsgamesres.s3.amazonaws.com</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>

--- a/LubanLaunchConfig/Datas/LaunchConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\games_Luckybillionspin_10\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -110,9 +110,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>MagicWealthRes</t>
-  </si>
-  <si>
     <t>SJYT20175638FDUUKNS38393753029039V32f700</t>
   </si>
   <si>
@@ -132,6 +129,10 @@
   </si>
   <si>
     <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>GTLuckyBillionSpinhRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -721,31 +722,31 @@
         <v>28</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="M4" s="1">
         <v>9</v>

--- a/LubanLaunchConfig/Datas/LaunchConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\games_bigwinroyale\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -110,9 +110,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>MagicWealthRes</t>
-  </si>
-  <si>
     <t>SJYT20175638FDUUKNS38393753029039V32f700</t>
   </si>
   <si>
@@ -131,7 +128,11 @@
     <t>English</t>
   </si>
   <si>
-    <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <t>https://slotapp.s3.amazonaws.com/resource</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BigWinRoyalehRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -721,31 +722,31 @@
         <v>28</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="M4" s="1">
         <v>9</v>
